--- a/sample-files/AgencyA_Submissions.xlsx
+++ b/sample-files/AgencyA_Submissions.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Short hair</t>
+          <t>Glasses</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Curly</t>
+          <t>Glases</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Braids</t>
+          <t>Hat</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Freckles</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -896,9 +896,9 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Bun</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Moustache</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -936,9 +936,9 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Moustache</t>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Freckels</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Scarf</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Glasses</t>
+          <t>Sombrero</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
